--- a/fase_2/precios/lista_kids_ropa.xlsx
+++ b/fase_2/precios/lista_kids_ropa.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B65"/>
+  <dimension ref="A1:B102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,580 +491,950 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1269575</t>
+          <t>1269584</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>490</v>
+        <v>520</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1269573</t>
+          <t>1269583</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>610</v>
+        <v>490</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1269586</t>
+          <t>1271735</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>610</v>
+        <v>400</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1269581</t>
+          <t>1271736</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>660</v>
+        <v>400</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1269582</t>
+          <t>1271737</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>760</v>
+        <v>400</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1269593</t>
+          <t>1269600</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>870</v>
+        <v>340</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1271728</t>
+          <t>1269597</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>670</v>
+        <v>400</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1197288</t>
+          <t>1269601</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>760</v>
+        <v>340</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1269580</t>
+          <t>1269598</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>720</v>
+        <v>400</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1269579</t>
+          <t>1197290</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>740</v>
+        <v>440</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1274139</t>
+          <t>1269575</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>760</v>
+        <v>490</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1269592</t>
+          <t>1269573</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>760</v>
+        <v>610</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1269591</t>
+          <t>1197287</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>760</v>
+        <v>530</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1269588</t>
+          <t>1197286</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>380</v>
+        <v>530</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1269587</t>
+          <t>1121401</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>380</v>
+        <v>670</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1274140</t>
+          <t>1228926</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>520</v>
+        <v>830</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1015535</t>
+          <t>1269599</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>420</v>
+        <v>400</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1104557</t>
+          <t>1271734</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>440</v>
+        <v>400</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>185393</t>
+          <t>1269586</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>440</v>
+        <v>610</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>822167</t>
+          <t>1269581</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>440</v>
+        <v>660</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>185390</t>
+          <t>1269582</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>440</v>
+        <v>760</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1269594</t>
+          <t>1269593</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>700</v>
+        <v>870</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1269596</t>
+          <t>1271728</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>690</v>
+        <v>670</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1236665</t>
+          <t>1269578</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>580</v>
+        <v>410</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1269574</t>
+          <t>1197511</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>510</v>
+        <v>720</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1198191</t>
+          <t>1197523</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>660</v>
+        <v>690</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1269572</t>
+          <t>1197288</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>510</v>
+        <v>760</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1071102</t>
+          <t>1269580</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>490</v>
+        <v>720</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1279041</t>
+          <t>1269579</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>510</v>
+        <v>740</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1071101</t>
+          <t>1274139</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>490</v>
+        <v>760</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1199810</t>
+          <t>1198206</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>700</v>
+        <v>520</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1236669</t>
+          <t>1269592</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>520</v>
+        <v>760</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1169181</t>
+          <t>1269591</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>590</v>
+        <v>760</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1279042</t>
+          <t>1269576</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>530</v>
+        <v>610</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1093845</t>
+          <t>1269588</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>530</v>
+        <v>380</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1093844</t>
+          <t>1269587</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>530</v>
+        <v>380</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1279060</t>
+          <t>1274140</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>410</v>
+        <v>520</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1279059</t>
+          <t>1015535</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>440</v>
+        <v>420</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1279057</t>
+          <t>1227649</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>530</v>
+        <v>520</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1279058</t>
+          <t>1160429</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>530</v>
+        <v>490</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1279056</t>
+          <t>1160428</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>690</v>
+        <v>410</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1279055</t>
+          <t>1102507</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>690</v>
+        <v>610</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1279043</t>
+          <t>1158825</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>580</v>
+        <v>870</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1117259</t>
+          <t>1104557</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>580</v>
+        <v>440</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1279053</t>
+          <t>1236987</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>760</v>
+        <v>520</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1117261</t>
+          <t>1236986</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>760</v>
+        <v>440</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1279054</t>
+          <t>1266622</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>910</v>
+        <v>440</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1284077</t>
+          <t>1266621</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>610</v>
+        <v>440</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1217120</t>
+          <t>1266620</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>610</v>
+        <v>440</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1181557</t>
+          <t>1266623</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>530</v>
+        <v>440</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1200601</t>
+          <t>185393</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>590</v>
+        <v>440</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1200605</t>
+          <t>822167</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>520</v>
+        <v>440</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1200604</t>
+          <t>185390</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>520</v>
+        <v>440</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1266577</t>
+          <t>1266582</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>420</v>
+        <v>450</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1266579</t>
+          <t>1266584</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>420</v>
+        <v>450</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1266578</t>
+          <t>1266583</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>420</v>
+        <v>450</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1266580</t>
+          <t>1266585</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>420</v>
+        <v>510</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
+          <t>1266586</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>1269594</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>1269596</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>1236665</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>1269574</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>1198191</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>1269572</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>1071102</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>1279041</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>1071101</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1199810</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>1236669</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>1169181</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>1279042</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>1093845</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>1093844</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>1279060</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>1279059</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>1279057</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>1279058</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>1279056</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>1279055</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>1279043</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>1117259</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>1279053</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>1117261</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>1279054</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>1284077</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>1217120</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>1181557</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>1200601</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>1200605</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>1200604</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>1266577</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>1266579</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>1266578</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>1266580</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
           <t>1266581</t>
         </is>
       </c>
-      <c r="B65" t="n">
+      <c r="B102" t="n">
         <v>420</v>
       </c>
     </row>
